--- a/PFOA extrapolation to humans/Data/Abraham et al.2024_oral_feces.xlsx
+++ b/PFOA extrapolation to humans/Data/Abraham et al.2024_oral_feces.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eviepapakyriakopoulou/Documents/Documents/NTUA Post-Doc/CHIASMA/PFOA extrapolation humans/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eviepapakyriakopoulou/Documents/GitHub/PFAS_PBK_models/PFOA extrapolation to humans/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F90F993-CE42-5E48-A66F-BB88FFE4EACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF6738C-470E-F04D-B361-C224EE9CEB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1040" yWindow="680" windowWidth="28360" windowHeight="18440" xr2:uid="{3744AC73-CAAE-7E42-A2FB-1EDC36DFABA9}"/>
+    <workbookView xWindow="1100" yWindow="680" windowWidth="28300" windowHeight="18440" xr2:uid="{3744AC73-CAAE-7E42-A2FB-1EDC36DFABA9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="9">
   <si>
     <t>Tissue</t>
   </si>
@@ -44,16 +44,7 @@
     <t>Type</t>
   </si>
   <si>
-    <t>ug</t>
-  </si>
-  <si>
     <t>Dose_ug</t>
-  </si>
-  <si>
-    <t>dose (mass)</t>
-  </si>
-  <si>
-    <t>absorbed</t>
   </si>
   <si>
     <t>oral</t>
@@ -62,40 +53,29 @@
     <t>Feces</t>
   </si>
   <si>
-    <t>feces_mass (g)</t>
-  </si>
-  <si>
-    <t>na</t>
-  </si>
-  <si>
-    <t>a) Amounts of feces not relevant for data evaluation (amounts of PFAS in a single portion do not represent the daily excretion)</t>
-  </si>
-  <si>
-    <t>concentration (ng/g)</t>
-  </si>
-  <si>
     <t>mode</t>
-  </si>
-  <si>
-    <t>repeated</t>
   </si>
   <si>
     <t>Time_h</t>
   </si>
   <si>
-    <t>Mass_(ng)</t>
+    <t>single</t>
+  </si>
+  <si>
+    <t>concentration_(ng/g)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
+    <numFmt numFmtId="172" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -120,12 +100,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -159,9 +133,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -171,13 +142,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -195,6 +169,1000 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$19</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>576</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>864</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>1392</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="General">
+                  <c:v>5424</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="General">
+                  <c:v>7440</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="General">
+                  <c:v>10104</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="General">
+                  <c:v>10128</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="General">
+                  <c:v>10152</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="General">
+                  <c:v>10176</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="General">
+                  <c:v>10200</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="General">
+                  <c:v>10224</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>2.3519804770631325E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7277000730407549E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.434439858303068E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5618895377846596E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.69382744492219E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.6107275922667324E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.6251160749545051E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.2634522772847164E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.3076279478818009E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.3404893403310219E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.9912329315133864E-4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.3298369221153481E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.2016372109842581E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.4260420459160052E-4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.6282776662311095E-4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.5485456015032798E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.4297179792081808E-3</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="0.00000">
+                  <c:v>5.9837924719720716E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E03E-0243-843F-53A56E317856}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1609559872"/>
+        <c:axId val="1609551808"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1609559872"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1609551808"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1609551808"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1609559872"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-GR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>805089</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>68035</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>511403</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>163966</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BB31159-7055-6B4D-9016-DB8848075E0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -514,447 +1482,445 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79597772-21D1-314A-89B1-40D073D89A86}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="3"/>
     <col min="2" max="2" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="3"/>
+    <col min="3" max="3" width="19.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="2">
-        <v>3.96</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="6">
-        <v>60</v>
-      </c>
-      <c r="C2" s="7">
-        <f>D2*E2</f>
-        <v>0.6115149240364145</v>
-      </c>
-      <c r="D2" s="6">
-        <v>260</v>
-      </c>
-      <c r="E2" s="8">
+      <c r="B2" s="5">
+        <v>24</v>
+      </c>
+      <c r="C2" s="8">
         <v>2.3519804770631325E-3</v>
       </c>
-      <c r="F2" s="5">
+      <c r="D2" s="4">
         <f>3.96*0.04/100</f>
         <v>1.5840000000000001E-3</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="4">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="L2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5">
+        <v>48</v>
+      </c>
+      <c r="C3" s="8">
+        <v>3.7277000730407549E-3</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.5840000000000001E-3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6">
+      <c r="G3" s="2"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5">
+        <v>72</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.434439858303068E-3</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.5840000000000001E-3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5">
+        <v>96</v>
+      </c>
+      <c r="C5" s="8">
+        <v>2.5618895377846596E-3</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.5840000000000001E-3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5">
         <v>120</v>
       </c>
-      <c r="C3" s="7">
-        <f t="shared" ref="C3:C13" si="0">D3*E3</f>
-        <v>0.60388741183260231</v>
-      </c>
-      <c r="D3" s="6">
-        <v>162</v>
-      </c>
-      <c r="E3" s="8">
-        <v>3.7277000730407549E-3</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="C6" s="8">
+        <v>2.69382744492219E-3</v>
+      </c>
+      <c r="D6" s="4">
         <v>1.5840000000000001E-3</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="7"/>
     </row>
-    <row r="4" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5">
+        <v>144</v>
+      </c>
+      <c r="C7" s="8">
+        <v>4.6107275922667324E-3</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.5840000000000001E-3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6">
-        <v>180</v>
-      </c>
-      <c r="C4" s="7">
-        <f t="shared" si="0"/>
-        <v>0.47049627352340628</v>
-      </c>
-      <c r="D4" s="6">
-        <v>328</v>
-      </c>
-      <c r="E4" s="8">
-        <v>1.434439858303068E-3</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="G7" s="2"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2">
+        <v>576</v>
+      </c>
+      <c r="C8" s="8">
+        <v>3.6251160749545051E-3</v>
+      </c>
+      <c r="D8" s="4">
         <v>1.5840000000000001E-3</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="E8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="2"/>
     </row>
-    <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2">
+        <v>864</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.2634522772847164E-3</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1.5840000000000001E-3</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6">
-        <v>240</v>
-      </c>
-      <c r="C5" s="7">
-        <f t="shared" si="0"/>
-        <v>0.51750168663250129</v>
-      </c>
-      <c r="D5" s="6">
-        <v>202</v>
-      </c>
-      <c r="E5" s="8">
-        <v>2.5618895377846596E-3</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="I9" s="9"/>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1392</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.3076279478818009E-3</v>
+      </c>
+      <c r="D10" s="4">
         <v>1.5840000000000001E-3</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="2"/>
     </row>
-    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2400</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2.3404893403310219E-3</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1.5840000000000001E-3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="6">
-        <v>300</v>
-      </c>
-      <c r="C6" s="7">
-        <f t="shared" si="0"/>
-        <v>0.6680692063407031</v>
-      </c>
-      <c r="D6" s="6">
-        <v>248</v>
-      </c>
-      <c r="E6" s="8">
-        <v>2.69382744492219E-3</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="I11" s="9"/>
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2">
+        <v>5424</v>
+      </c>
+      <c r="C12" s="8">
+        <v>8.9912329315133864E-4</v>
+      </c>
+      <c r="D12" s="4">
         <v>1.5840000000000001E-3</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="L6" s="3" t="s">
+      <c r="E12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="6">
-        <v>25260</v>
-      </c>
-      <c r="N6" s="7">
-        <f t="shared" ref="N6:N7" si="1">O6*P6</f>
-        <v>0.17409044362888124</v>
-      </c>
-      <c r="O6" s="6">
-        <v>58</v>
-      </c>
-      <c r="P6" s="9">
-        <v>3.0015593729117453E-3</v>
-      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="2"/>
     </row>
-    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+    <row r="13" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2">
+        <v>7440</v>
+      </c>
+      <c r="C13" s="8">
+        <v>3.3298369221153481E-3</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1.5840000000000001E-3</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
-        <v>360</v>
-      </c>
-      <c r="C7" s="7">
-        <f t="shared" si="0"/>
-        <v>0.4149654833040059</v>
-      </c>
-      <c r="D7" s="6">
-        <v>90</v>
-      </c>
-      <c r="E7" s="8">
-        <v>4.6107275922667324E-3</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1.5840000000000001E-3</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="L7" s="3" t="s">
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2">
+        <v>10104</v>
+      </c>
+      <c r="C14" s="8">
+        <v>3.2016372109842581E-3</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1.001584</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M7" s="6">
-        <v>25272</v>
-      </c>
-      <c r="N7" s="7">
-        <f t="shared" si="1"/>
-        <v>0.42181266608303891</v>
-      </c>
-      <c r="O7" s="6">
-        <v>124</v>
-      </c>
-      <c r="P7" s="9">
-        <v>3.4017150490567656E-3</v>
-      </c>
+      <c r="I14" s="9"/>
     </row>
-    <row r="8" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="15" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2">
+        <v>10128</v>
+      </c>
+      <c r="C15" s="8">
+        <v>5.4260420459160052E-4</v>
+      </c>
+      <c r="D15" s="4">
+        <v>3.0015839999999998</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
-        <v>25260</v>
-      </c>
-      <c r="C8" s="7">
-        <f t="shared" si="0"/>
-        <v>0.18569495823708707</v>
-      </c>
-      <c r="D8" s="6">
-        <v>58</v>
-      </c>
-      <c r="E8" s="10">
-        <f>(0.00300155937291175+0.00340171504905677)/2</f>
-        <v>3.2016372109842598E-3</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1.5840000000000001E-3</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="3">
-        <f>(0.00300155937291175+0.00340171504905677)/2</f>
-        <v>3.2016372109842598E-3</v>
-      </c>
+      <c r="I15" s="9"/>
     </row>
-    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+    <row r="16" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2">
+        <v>10152</v>
+      </c>
+      <c r="C16" s="8">
+        <v>8.6282776662311095E-4</v>
+      </c>
+      <c r="D16" s="4">
+        <v>4.0015840000000003</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="6">
-        <v>25320</v>
-      </c>
-      <c r="C9" s="7">
-        <f t="shared" si="0"/>
-        <v>0.12208594603311011</v>
-      </c>
-      <c r="D9" s="6">
-        <v>225</v>
-      </c>
-      <c r="E9" s="9">
-        <v>5.4260420459160052E-4</v>
-      </c>
-      <c r="F9" s="5">
-        <v>1.5840000000000001E-3</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="2"/>
+      <c r="I16" s="9"/>
     </row>
-    <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2">
+        <v>10176</v>
+      </c>
+      <c r="C17" s="8">
+        <v>8.5485456015032798E-4</v>
+      </c>
+      <c r="D17" s="4">
+        <v>5.0015840000000003</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="6">
-        <v>25380</v>
-      </c>
-      <c r="C10" s="7">
-        <f t="shared" si="0"/>
-        <v>0.22692370262187819</v>
-      </c>
-      <c r="D10" s="6">
-        <v>263</v>
-      </c>
-      <c r="E10" s="9">
-        <v>8.6282776662311095E-4</v>
-      </c>
-      <c r="F10" s="5">
-        <v>1.5840000000000001E-3</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="2"/>
+      <c r="I17" s="9"/>
     </row>
-    <row r="11" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+    <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2">
+        <v>10200</v>
+      </c>
+      <c r="C18" s="8">
+        <v>2.4297179792081808E-3</v>
+      </c>
+      <c r="D18" s="4">
+        <v>6.0015840000000003</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="6">
-        <v>25440</v>
-      </c>
-      <c r="C11" s="7">
-        <f t="shared" si="0"/>
-        <v>0.14105100242480412</v>
-      </c>
-      <c r="D11" s="6">
-        <v>165</v>
-      </c>
-      <c r="E11" s="9">
-        <v>8.5485456015032798E-4</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1.5840000000000001E-3</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="2"/>
+      <c r="I18" s="9"/>
     </row>
-    <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2">
+        <v>10224</v>
+      </c>
+      <c r="C19" s="10">
+        <v>5.9837924719720716E-4</v>
+      </c>
+      <c r="D19" s="4">
+        <v>7.0015840000000003</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="6">
-        <v>25500</v>
-      </c>
-      <c r="C12" s="7">
-        <f t="shared" si="0"/>
-        <v>0.34501995304756167</v>
-      </c>
-      <c r="D12" s="6">
-        <v>142</v>
-      </c>
-      <c r="E12" s="9">
-        <v>2.4297179792081808E-3</v>
-      </c>
-      <c r="F12" s="5">
-        <v>1.5840000000000001E-3</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6">
-        <v>25560</v>
-      </c>
-      <c r="C13" s="7">
-        <f t="shared" si="0"/>
-        <v>0.13523370986656882</v>
-      </c>
-      <c r="D13" s="6">
-        <v>226</v>
-      </c>
-      <c r="E13" s="9">
-        <v>5.9837924719720716E-4</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1.5840000000000001E-3</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="H14" s="2"/>
+      <c r="I19" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>